--- a/eDrops/src/main/resources/static/energyData/SsbEl.xlsx
+++ b/eDrops/src/main/resources/static/energyData/SsbEl.xlsx
@@ -1,47 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="13">
+  <si>
+    <t xml:space="preserve">Produksjon i alt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vannkraftproduksjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vindkraftproduksjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solkraftproduksjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varmekraftproduksjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eksport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruttoforbruk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forbruk i kraftstasjonene (-2019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pumpekraftforbruk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap og statistisk differanse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nettoforbruk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">..</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,7 +101,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -61,56 +109,84 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -118,1025 +194,926 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="str">
-        <v>Produksjon i alt</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Vannkraftproduksjon</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Vindkraftproduksjon</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Solkraftproduksjon</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Varmekraftproduksjon</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Import</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Eksport</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Bruttoforbruk</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Forbruk i kraftstasjonene (-2019)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Pumpekraftforbruk</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Tap og statistisk differanse</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Nettoforbruk</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
         <v>2008</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0" t="n">
         <v>142108</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0" t="n">
         <v>139981</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0" t="n">
         <v>913</v>
       </c>
-      <c r="E2" t="str">
-        <v>..</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="0" t="n">
         <v>1214</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="0" t="n">
         <v>3414</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0" t="n">
         <v>17291</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0" t="n">
         <v>128231</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="0" t="n">
         <v>637</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="0" t="n">
         <v>1338</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="0" t="n">
         <v>9948</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="0" t="n">
         <v>116308</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
         <v>2009</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0" t="n">
         <v>131773</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0" t="n">
         <v>126077</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0" t="n">
         <v>977</v>
       </c>
-      <c r="E3" t="str">
-        <v>..</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="0" t="n">
         <v>4719</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="0" t="n">
         <v>5650</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0" t="n">
         <v>14633</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="0" t="n">
         <v>122790</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="0" t="n">
         <v>659</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="0" t="n">
         <v>1135</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="0" t="n">
         <v>8629</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="0" t="n">
         <v>112367</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
         <v>2010</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0" t="n">
         <v>123630</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0" t="n">
         <v>117152</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0" t="n">
         <v>879</v>
       </c>
-      <c r="E4" t="str">
-        <v>..</v>
-      </c>
-      <c r="F4">
+      <c r="E4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="0" t="n">
         <v>5599</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="0" t="n">
         <v>14673</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="0" t="n">
         <v>7123</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="0" t="n">
         <v>131180</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="0" t="n">
         <v>560</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="0" t="n">
         <v>574</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="0" t="n">
         <v>9490</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0" t="n">
         <v>120556</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
         <v>2011</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0" t="n">
         <v>127631</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0" t="n">
         <v>121553</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0" t="n">
         <v>1283</v>
       </c>
-      <c r="E5" t="str">
-        <v>..</v>
-      </c>
-      <c r="F5">
+      <c r="E5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="0" t="n">
         <v>4795</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="0" t="n">
         <v>11255</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="0" t="n">
         <v>14329</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="0" t="n">
         <v>124557</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="0" t="n">
         <v>544</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="0" t="n">
         <v>1807</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="0" t="n">
         <v>7263</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="0" t="n">
         <v>114943</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
         <v>2012</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0" t="n">
         <v>147716</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0" t="n">
         <v>142810</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0" t="n">
         <v>1548</v>
       </c>
-      <c r="E6" t="str">
-        <v>..</v>
-      </c>
-      <c r="F6">
+      <c r="E6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <v>3358</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="0" t="n">
         <v>4190</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0" t="n">
         <v>22006</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="0" t="n">
         <v>129900</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="0" t="n">
         <v>560</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="0" t="n">
         <v>1536</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="0" t="n">
         <v>9098</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="0" t="n">
         <v>118706</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
         <v>2013</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0" t="n">
         <v>133975</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0" t="n">
         <v>128699</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0" t="n">
         <v>1881</v>
       </c>
-      <c r="E7" t="str">
-        <v>..</v>
-      </c>
-      <c r="F7">
+      <c r="E7" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="0" t="n">
         <v>3395</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="0" t="n">
         <v>10135</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="0" t="n">
         <v>15140</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="0" t="n">
         <v>128970</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="0" t="n">
         <v>620</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="0" t="n">
         <v>786</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="0" t="n">
         <v>8024</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="0" t="n">
         <v>119540</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0" t="n">
         <v>141968</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0" t="n">
         <v>136181</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="0" t="n">
         <v>2217</v>
       </c>
-      <c r="E8" t="str">
-        <v>..</v>
-      </c>
-      <c r="F8">
+      <c r="E8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="0" t="n">
         <v>3570</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="0" t="n">
         <v>6347</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="0" t="n">
         <v>21932</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="0" t="n">
         <v>126383</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="0" t="n">
         <v>692</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="0" t="n">
         <v>997</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="0" t="n">
         <v>7637</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="0" t="n">
         <v>117057</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
         <v>2015</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0" t="n">
         <v>144511</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0" t="n">
         <v>138450</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0" t="n">
         <v>2515</v>
       </c>
-      <c r="E9" t="str">
-        <v>..</v>
-      </c>
-      <c r="F9">
+      <c r="E9" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="0" t="n">
         <v>3546</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="0" t="n">
         <v>7411</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="0" t="n">
         <v>22038</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="0" t="n">
         <v>129884</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="0" t="n">
         <v>693</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="0" t="n">
         <v>1612</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="0" t="n">
         <v>7530</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="0" t="n">
         <v>120049</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0" t="n">
         <v>148989</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0" t="n">
         <v>143417</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0" t="n">
         <v>2116</v>
       </c>
-      <c r="E10" t="str">
-        <v>..</v>
-      </c>
-      <c r="F10">
+      <c r="E10" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="0" t="n">
         <v>3456</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="0" t="n">
         <v>5741</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="0" t="n">
         <v>22151</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="0" t="n">
         <v>132579</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="0" t="n">
         <v>563</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="0" t="n">
         <v>872</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="0" t="n">
         <v>7697</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="0" t="n">
         <v>123447</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0" t="n">
         <v>149402</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0" t="n">
         <v>143112</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="0" t="n">
         <v>2854</v>
       </c>
-      <c r="E11" t="str">
-        <v>..</v>
-      </c>
-      <c r="F11">
+      <c r="E11" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="0" t="n">
         <v>3436</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="0" t="n">
         <v>6112</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="0" t="n">
         <v>21276</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="0" t="n">
         <v>134238</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="0" t="n">
         <v>718</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="0" t="n">
         <v>1065</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="0" t="n">
         <v>7625</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="0" t="n">
         <v>124830</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="0" t="n">
         <v>147057</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0" t="n">
         <v>139704</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="0" t="n">
         <v>3877</v>
       </c>
-      <c r="E12" t="str">
-        <v>..</v>
-      </c>
-      <c r="F12">
+      <c r="E12" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="0" t="n">
         <v>3476</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="0" t="n">
         <v>8340</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="0" t="n">
         <v>18489</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="0" t="n">
         <v>136908</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="0" t="n">
         <v>765</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="0" t="n">
         <v>1031</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="0" t="n">
         <v>7564</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="0" t="n">
         <v>127548</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="0" t="n">
         <v>134882</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0" t="n">
         <v>126030</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="0" t="n">
         <v>5525</v>
       </c>
-      <c r="E13" t="str">
-        <v>..</v>
-      </c>
-      <c r="F13">
+      <c r="E13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="0" t="n">
         <v>3328</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="0" t="n">
         <v>12353</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="0" t="n">
         <v>12309</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="0" t="n">
         <v>134926</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="0" t="n">
         <v>825</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="0" t="n">
         <v>1054</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="0" t="n">
         <v>6996</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="0" t="n">
         <v>126051</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="0" t="n">
         <v>154197</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0" t="n">
         <v>141590</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="0" t="n">
         <v>9911</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="0" t="n">
         <v>2670</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="0" t="n">
         <v>4496</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="0" t="n">
         <v>24968</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="0" t="n">
         <v>133724</v>
       </c>
-      <c r="J14" t="str">
-        <v>..</v>
-      </c>
-      <c r="K14">
+      <c r="J14" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <v>952</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="0" t="n">
         <v>6967</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="0" t="n">
         <v>125806</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="0" t="n">
         <v>157113</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0" t="n">
         <v>143699</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="0" t="n">
         <v>11768</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="0" t="n">
         <v>1612</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="0" t="n">
         <v>8235</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="0" t="n">
         <v>25819</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="0" t="n">
         <v>139529</v>
       </c>
-      <c r="J15" t="str">
-        <v>..</v>
-      </c>
-      <c r="K15">
+      <c r="J15" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <v>576</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="0" t="n">
         <v>7653</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="0" t="n">
         <v>131300</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
         <v>2022</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="0" t="n">
         <v>145942</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="0" t="n">
         <v>128749</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="0" t="n">
         <v>14810</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="0" t="n">
         <v>63</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="0" t="n">
         <v>2319</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="0" t="n">
         <v>13270</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="0" t="n">
         <v>25792</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="0" t="n">
         <v>133420</v>
       </c>
-      <c r="J16" t="str">
-        <v>..</v>
-      </c>
-      <c r="K16">
+      <c r="J16" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <v>1609</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="0" t="n">
         <v>7277</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="0" t="n">
         <v>124534</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
         <v>2023</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="0" t="n">
         <v>153973</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="0" t="n">
         <v>137315</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="0" t="n">
         <v>13965</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="0" t="n">
         <v>165</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="0" t="n">
         <v>2528</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="0" t="n">
         <v>13240</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="0" t="n">
         <v>30978</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="0" t="n">
         <v>136235</v>
       </c>
-      <c r="J17" t="str">
-        <v>..</v>
-      </c>
-      <c r="K17">
+      <c r="J17" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <v>1786</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="0" t="n">
         <v>7949</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="0" t="n">
         <v>126500</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
         <v>2024</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="0" t="n">
         <v>157136</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="0" t="n">
         <v>139984</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="0" t="n">
         <v>14545</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="0" t="n">
         <v>251</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="0" t="n">
         <v>2357</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="0" t="n">
         <v>14685</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="0" t="n">
         <v>33124</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="0" t="n">
         <v>138698</v>
       </c>
-      <c r="J18" t="str">
-        <v>..</v>
-      </c>
-      <c r="K18">
+      <c r="J18" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <v>1558</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="0" t="n">
         <v>7806</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="0" t="n">
         <v>129334</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>161793</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>145476</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>13899</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>348</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>2070</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>11515</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>34315</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>138993</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="0" t="n">
+        <v>1417</v>
+      </c>
+      <c r="L19" s="0" t="n">
+        <v>7451</v>
+      </c>
+      <c r="M19" s="0" t="n">
+        <v>130125</v>
+      </c>
+    </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M18"/>
-  </ignoredErrors>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>